--- a/results/supp_data/Supplementary Data 1.xlsx
+++ b/results/supp_data/Supplementary Data 1.xlsx
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stable identifier used across Tables S1 and S4.</t>
+          <t>Stable identifier used across Supplementary Data 1 and 4.</t>
         </is>
       </c>
     </row>
